--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/32.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/32.xlsx
@@ -426,13 +426,13 @@
         <v>-14.97122417299956</v>
       </c>
       <c r="E2">
-        <v>-6.650976380247064</v>
+        <v>-8.260287359196925</v>
       </c>
       <c r="F2">
-        <v>-0.3213147789480503</v>
+        <v>-1.82477114824035</v>
       </c>
       <c r="G2">
-        <v>-9.718392288115281</v>
+        <v>-9.51235055484212</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.87150903443578</v>
       </c>
       <c r="E3">
-        <v>-7.266894130030309</v>
+        <v>-7.337221331369429</v>
       </c>
       <c r="F3">
-        <v>-0.1429847417518222</v>
+        <v>-1.574924119314707</v>
       </c>
       <c r="G3">
-        <v>-9.468323609715354</v>
+        <v>-8.878344668070756</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.78386198884657</v>
       </c>
       <c r="E4">
-        <v>-7.921023143490276</v>
+        <v>-8.823439329842795</v>
       </c>
       <c r="F4">
-        <v>-0.4729150277034914</v>
+        <v>-1.520241129613456</v>
       </c>
       <c r="G4">
-        <v>-8.667727760862324</v>
+        <v>-8.947031866919556</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.65978602160401</v>
       </c>
       <c r="E5">
-        <v>-8.942257430856049</v>
+        <v>-11.15223425913132</v>
       </c>
       <c r="F5">
-        <v>-0.1542924019880598</v>
+        <v>-1.74188314803808</v>
       </c>
       <c r="G5">
-        <v>-8.250314315997777</v>
+        <v>-9.615629644030763</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.46399366785711</v>
       </c>
       <c r="E6">
-        <v>-9.62822161658994</v>
+        <v>-9.34597541711387</v>
       </c>
       <c r="F6">
-        <v>0.3376430805834877</v>
+        <v>-1.546289132657647</v>
       </c>
       <c r="G6">
-        <v>-7.966345651275712</v>
+        <v>-8.74092061219007</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.1714333225795</v>
       </c>
       <c r="E7">
-        <v>-11.22169652193498</v>
+        <v>-10.90754722307487</v>
       </c>
       <c r="F7">
-        <v>0.418574412127232</v>
+        <v>-1.570192797892332</v>
       </c>
       <c r="G7">
-        <v>-8.579680491699866</v>
+        <v>-8.115191089266883</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.76695810798034</v>
       </c>
       <c r="E8">
-        <v>-11.42550049465018</v>
+        <v>-12.6646721221091</v>
       </c>
       <c r="F8">
-        <v>0.07172064476317688</v>
+        <v>-1.50510961144439</v>
       </c>
       <c r="G8">
-        <v>-7.826842572796363</v>
+        <v>-8.342208439076867</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.26316770660074</v>
       </c>
       <c r="E9">
-        <v>-12.68095651464068</v>
+        <v>-13.95572194779989</v>
       </c>
       <c r="F9">
-        <v>0.3556664457541463</v>
+        <v>-1.277103470798573</v>
       </c>
       <c r="G9">
-        <v>-6.855796665762878</v>
+        <v>-7.354642909802418</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.68626232968933</v>
       </c>
       <c r="E10">
-        <v>-13.70821367243666</v>
+        <v>-14.97658942877104</v>
       </c>
       <c r="F10">
-        <v>0.3959646346254608</v>
+        <v>-1.022022293822403</v>
       </c>
       <c r="G10">
-        <v>-6.319614089131438</v>
+        <v>-5.845219534444955</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.06962493340333</v>
       </c>
       <c r="E11">
-        <v>-15.21328370820395</v>
+        <v>-15.66160263496332</v>
       </c>
       <c r="F11">
-        <v>0.3380643463569946</v>
+        <v>-1.227219901874061</v>
       </c>
       <c r="G11">
-        <v>-5.439591631700214</v>
+        <v>-6.282185061264438</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.45252702024439</v>
       </c>
       <c r="E12">
-        <v>-15.72977428267479</v>
+        <v>-16.17260017046285</v>
       </c>
       <c r="F12">
-        <v>0.6601727087923083</v>
+        <v>-1.273972484203749</v>
       </c>
       <c r="G12">
-        <v>-5.044835560506439</v>
+        <v>-6.364720272104008</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.85313165270199</v>
       </c>
       <c r="E13">
-        <v>-15.3015753659315</v>
+        <v>-15.57136826188648</v>
       </c>
       <c r="F13">
-        <v>0.6810095275217452</v>
+        <v>-0.7179238350574665</v>
       </c>
       <c r="G13">
-        <v>-4.266304497672652</v>
+        <v>-6.176174772005896</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.29037426673401</v>
       </c>
       <c r="E14">
-        <v>-17.57229714454567</v>
+        <v>-18.29206186027281</v>
       </c>
       <c r="F14">
-        <v>0.7832424954811078</v>
+        <v>-0.3596507561901353</v>
       </c>
       <c r="G14">
-        <v>-3.93213140984754</v>
+        <v>-5.238754076014788</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.767692300329813</v>
       </c>
       <c r="E15">
-        <v>-18.06970472954818</v>
+        <v>-18.68531001462489</v>
       </c>
       <c r="F15">
-        <v>0.5464966737409379</v>
+        <v>-0.5912843752352666</v>
       </c>
       <c r="G15">
-        <v>-2.711238630965258</v>
+        <v>-4.420930148175391</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.27249798305864</v>
       </c>
       <c r="E16">
-        <v>-18.61274574712598</v>
+        <v>-18.45349743017225</v>
       </c>
       <c r="F16">
-        <v>0.9737987423445285</v>
+        <v>-0.6907205185479631</v>
       </c>
       <c r="G16">
-        <v>-2.527059740433445</v>
+        <v>-4.174681839327783</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.796938119807157</v>
       </c>
       <c r="E17">
-        <v>-20.29722033765515</v>
+        <v>-19.8479051466141</v>
       </c>
       <c r="F17">
-        <v>0.9115717695150817</v>
+        <v>-0.05943237691802551</v>
       </c>
       <c r="G17">
-        <v>-1.995727113017037</v>
+        <v>-3.609515436500023</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.326714659379128</v>
       </c>
       <c r="E18">
-        <v>-20.58691587687385</v>
+        <v>-21.45513755599444</v>
       </c>
       <c r="F18">
-        <v>0.8540262313716739</v>
+        <v>0.4688087719120136</v>
       </c>
       <c r="G18">
-        <v>-1.141344830787468</v>
+        <v>-2.661461268236776</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.853178733222696</v>
       </c>
       <c r="E19">
-        <v>-22.26424000694491</v>
+        <v>-21.25460314151278</v>
       </c>
       <c r="F19">
-        <v>1.308472227512939</v>
+        <v>0.2815988956479165</v>
       </c>
       <c r="G19">
-        <v>-1.639303848622483</v>
+        <v>-2.825372998977171</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.374878551527336</v>
       </c>
       <c r="E20">
-        <v>-22.77531452650257</v>
+        <v>-23.21120279211088</v>
       </c>
       <c r="F20">
-        <v>1.687989929382933</v>
+        <v>0.5041452101502563</v>
       </c>
       <c r="G20">
-        <v>-0.510096628450317</v>
+        <v>-2.70672966794077</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.88235231798116</v>
       </c>
       <c r="E21">
-        <v>-22.67383142399067</v>
+        <v>-22.37526913266497</v>
       </c>
       <c r="F21">
-        <v>1.563992091027685</v>
+        <v>0.9549447234212218</v>
       </c>
       <c r="G21">
-        <v>-0.7511010331637201</v>
+        <v>-2.86748644878224</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.381912656069016</v>
       </c>
       <c r="E22">
-        <v>-24.17569982863455</v>
+        <v>-24.77378444777559</v>
       </c>
       <c r="F22">
-        <v>2.002135418475417</v>
+        <v>1.367889706048396</v>
       </c>
       <c r="G22">
-        <v>-0.7404179027084919</v>
+        <v>-1.938401706459017</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.880653435040714</v>
       </c>
       <c r="E23">
-        <v>-24.41801394431098</v>
+        <v>-24.99037230261445</v>
       </c>
       <c r="F23">
-        <v>2.208961076208147</v>
+        <v>1.013467408114456</v>
       </c>
       <c r="G23">
-        <v>0.3312950730831516</v>
+        <v>-2.93744158657258</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.387813135369688</v>
       </c>
       <c r="E24">
-        <v>-24.53327266475421</v>
+        <v>-25.4533861275287</v>
       </c>
       <c r="F24">
-        <v>2.042182589959134</v>
+        <v>0.9638261461950062</v>
       </c>
       <c r="G24">
-        <v>0.4287244283039026</v>
+        <v>-2.738706227304591</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.923140793245401</v>
       </c>
       <c r="E25">
-        <v>-24.77017978246548</v>
+        <v>-25.25435063794357</v>
       </c>
       <c r="F25">
-        <v>2.355393692561509</v>
+        <v>1.407350906343401</v>
       </c>
       <c r="G25">
-        <v>-0.8016332002751555</v>
+        <v>-1.988546539742358</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.501796064599243</v>
       </c>
       <c r="E26">
-        <v>-25.52230950192545</v>
+        <v>-26.48064328532468</v>
       </c>
       <c r="F26">
-        <v>2.363545026908276</v>
+        <v>1.971656998132784</v>
       </c>
       <c r="G26">
-        <v>0.3180826858359203</v>
+        <v>-2.07910982351466</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.139020115855111</v>
       </c>
       <c r="E27">
-        <v>-25.62795880052439</v>
+        <v>-26.0823821102461</v>
       </c>
       <c r="F27">
-        <v>2.449589353000016</v>
+        <v>1.678623892599024</v>
       </c>
       <c r="G27">
-        <v>-0.4834699106779588</v>
+        <v>-2.732363222051347</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.84555286280202</v>
       </c>
       <c r="E28">
-        <v>-25.36265815078503</v>
+        <v>-25.86067707977858</v>
       </c>
       <c r="F28">
-        <v>2.573604612120333</v>
+        <v>1.672851284537247</v>
       </c>
       <c r="G28">
-        <v>-0.2630306148545083</v>
+        <v>-3.430265948276185</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.614813668924058</v>
       </c>
       <c r="E29">
-        <v>-25.78680408329145</v>
+        <v>-26.45947719781283</v>
       </c>
       <c r="F29">
-        <v>2.500630610948714</v>
+        <v>1.691366390394649</v>
       </c>
       <c r="G29">
-        <v>-0.7108017623141719</v>
+        <v>-2.624128246190415</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.440343444386234</v>
       </c>
       <c r="E30">
-        <v>-25.95982801817652</v>
+        <v>-25.06396000523909</v>
       </c>
       <c r="F30">
-        <v>2.591981935563092</v>
+        <v>1.64147490294056</v>
       </c>
       <c r="G30">
-        <v>-0.445103998423345</v>
+        <v>-2.630848653635136</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.310898630714003</v>
       </c>
       <c r="E31">
-        <v>-25.68953246160669</v>
+        <v>-25.6546450978516</v>
       </c>
       <c r="F31">
-        <v>2.536694762055101</v>
+        <v>1.886209729171165</v>
       </c>
       <c r="G31">
-        <v>-0.5823592164815284</v>
+        <v>-2.575807523499213</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.213023367442683</v>
       </c>
       <c r="E32">
-        <v>-24.53935893382052</v>
+        <v>-24.3736847122499</v>
       </c>
       <c r="F32">
-        <v>2.53605652857118</v>
+        <v>1.716873557868717</v>
       </c>
       <c r="G32">
-        <v>-0.746899950874385</v>
+        <v>-3.937914932904647</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.138804584377674</v>
       </c>
       <c r="E33">
-        <v>-24.42301790808946</v>
+        <v>-23.67183011122309</v>
       </c>
       <c r="F33">
-        <v>2.479529313331399</v>
+        <v>1.717925138596569</v>
       </c>
       <c r="G33">
-        <v>-1.650884136918854</v>
+        <v>-2.568799098592576</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.080245525680593</v>
       </c>
       <c r="E34">
-        <v>-25.30165960590171</v>
+        <v>-24.95659441499123</v>
       </c>
       <c r="F34">
-        <v>2.741140109796926</v>
+        <v>1.382863645478876</v>
       </c>
       <c r="G34">
-        <v>-1.112668885326301</v>
+        <v>-3.298009653982301</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.032708196595505</v>
       </c>
       <c r="E35">
-        <v>-23.57048739140544</v>
+        <v>-23.59324297329398</v>
       </c>
       <c r="F35">
-        <v>2.778889323997341</v>
+        <v>1.389510459205975</v>
       </c>
       <c r="G35">
-        <v>-1.695990319891424</v>
+        <v>-3.450788020074127</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.995244670836708</v>
       </c>
       <c r="E36">
-        <v>-24.07469221589346</v>
+        <v>-23.68180633946199</v>
       </c>
       <c r="F36">
-        <v>2.859851537806436</v>
+        <v>1.466969515530119</v>
       </c>
       <c r="G36">
-        <v>-1.869913140342575</v>
+        <v>-3.024499002618794</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.966192706393856</v>
       </c>
       <c r="E37">
-        <v>-22.53096259752268</v>
+        <v>-22.1546011227452</v>
       </c>
       <c r="F37">
-        <v>2.493149184204178</v>
+        <v>1.920470039239866</v>
       </c>
       <c r="G37">
-        <v>-1.416931194204098</v>
+        <v>-2.170583507310262</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.948388475246342</v>
       </c>
       <c r="E38">
-        <v>-22.85358919972515</v>
+        <v>-22.95832827504856</v>
       </c>
       <c r="F38">
-        <v>2.824072453764828</v>
+        <v>1.052827251230872</v>
       </c>
       <c r="G38">
-        <v>-1.332475866951751</v>
+        <v>-3.01956297921974</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.945099562568466</v>
       </c>
       <c r="E39">
-        <v>-22.08763857759378</v>
+        <v>-23.86129693523001</v>
       </c>
       <c r="F39">
-        <v>2.550469836107594</v>
+        <v>1.349363514249585</v>
       </c>
       <c r="G39">
-        <v>-1.724831792629554</v>
+        <v>-3.104743315945188</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.956234089470397</v>
       </c>
       <c r="E40">
-        <v>-21.83663884877063</v>
+        <v>-21.99072923382963</v>
       </c>
       <c r="F40">
-        <v>2.586480141212856</v>
+        <v>1.918887917030342</v>
       </c>
       <c r="G40">
-        <v>-1.54247370214434</v>
+        <v>-2.080136092631835</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.982028492517512</v>
       </c>
       <c r="E41">
-        <v>-20.80618458832524</v>
+        <v>-20.97883265986767</v>
       </c>
       <c r="F41">
-        <v>2.570939235064649</v>
+        <v>1.534357785937983</v>
       </c>
       <c r="G41">
-        <v>-1.682476673000119</v>
+        <v>-3.246563776302027</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.023199072060356</v>
       </c>
       <c r="E42">
-        <v>-19.64864323332859</v>
+        <v>-20.85978813515404</v>
       </c>
       <c r="F42">
-        <v>2.568717295665287</v>
+        <v>1.327999321450307</v>
       </c>
       <c r="G42">
-        <v>-1.376929872453085</v>
+        <v>-3.222181608405295</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.080438560124052</v>
       </c>
       <c r="E43">
-        <v>-19.11291117279917</v>
+        <v>-20.33113860797261</v>
       </c>
       <c r="F43">
-        <v>2.86799336991771</v>
+        <v>1.621529710641516</v>
       </c>
       <c r="G43">
-        <v>-0.7587848093603685</v>
+        <v>-2.953130261883186</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.159475412356023</v>
       </c>
       <c r="E44">
-        <v>-18.31340455827096</v>
+        <v>-19.35625325207534</v>
       </c>
       <c r="F44">
-        <v>2.784362611641099</v>
+        <v>0.7097902151230262</v>
       </c>
       <c r="G44">
-        <v>-0.629292820591776</v>
+        <v>-3.201699263153824</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.265300366065866</v>
       </c>
       <c r="E45">
-        <v>-19.34374560686615</v>
+        <v>-18.56326311164417</v>
       </c>
       <c r="F45">
-        <v>2.890030637731051</v>
+        <v>1.201686105046688</v>
       </c>
       <c r="G45">
-        <v>-1.111056649648676</v>
+        <v>-2.75074999197646</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.40139431664232</v>
       </c>
       <c r="E46">
-        <v>-17.80045072200011</v>
+        <v>-18.15623028241274</v>
       </c>
       <c r="F46">
-        <v>2.760771728324714</v>
+        <v>1.471278779326029</v>
       </c>
       <c r="G46">
-        <v>-0.876521050919009</v>
+        <v>-2.478775433743174</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.574634190105265</v>
       </c>
       <c r="E47">
-        <v>-16.22194242325043</v>
+        <v>-17.02168451842703</v>
       </c>
       <c r="F47">
-        <v>3.014848835750495</v>
+        <v>0.8382731086307977</v>
       </c>
       <c r="G47">
-        <v>-1.604589468097686</v>
+        <v>-2.926341327379403</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.786531192021433</v>
       </c>
       <c r="E48">
-        <v>-15.83864332629319</v>
+        <v>-17.2223366732329</v>
       </c>
       <c r="F48">
-        <v>2.641667541248174</v>
+        <v>1.265043843899758</v>
       </c>
       <c r="G48">
-        <v>-0.6476762799713489</v>
+        <v>-2.905018103560958</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.038556541871179</v>
       </c>
       <c r="E49">
-        <v>-15.04052695328534</v>
+        <v>-16.39746154731372</v>
       </c>
       <c r="F49">
-        <v>2.994599571915686</v>
+        <v>1.362503522229986</v>
       </c>
       <c r="G49">
-        <v>-0.8113330987052201</v>
+        <v>-2.795568157487113</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.335272737319089</v>
       </c>
       <c r="E50">
-        <v>-15.33670726728301</v>
+        <v>-15.7349774993096</v>
       </c>
       <c r="F50">
-        <v>3.096075528447469</v>
+        <v>1.426461485625008</v>
       </c>
       <c r="G50">
-        <v>-1.093613385202256</v>
+        <v>-2.646044057660391</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.675153620813925</v>
       </c>
       <c r="E51">
-        <v>-14.24791720467081</v>
+        <v>-14.90731736187571</v>
       </c>
       <c r="F51">
-        <v>2.789506488454447</v>
+        <v>0.9331228396123816</v>
       </c>
       <c r="G51">
-        <v>-1.0486263818691</v>
+        <v>-3.553808886710707</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.059286701568737</v>
       </c>
       <c r="E52">
-        <v>-13.60206624169686</v>
+        <v>-15.69202039487284</v>
       </c>
       <c r="F52">
-        <v>2.627914639078498</v>
+        <v>1.132137659770164</v>
       </c>
       <c r="G52">
-        <v>-1.43127578802576</v>
+        <v>-3.68706827630299</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.484490237082178</v>
       </c>
       <c r="E53">
-        <v>-12.46531963934343</v>
+        <v>-14.94302437942619</v>
       </c>
       <c r="F53">
-        <v>3.117172074947038</v>
+        <v>0.9943219873027083</v>
       </c>
       <c r="G53">
-        <v>-1.798928422889522</v>
+        <v>-2.804215302435689</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.942107531177586</v>
       </c>
       <c r="E54">
-        <v>-11.95925814051227</v>
+        <v>-14.27045089133298</v>
       </c>
       <c r="F54">
-        <v>3.014243860090797</v>
+        <v>1.068176528963311</v>
       </c>
       <c r="G54">
-        <v>-1.908285673688267</v>
+        <v>-4.435883882376279</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.42965581221972</v>
       </c>
       <c r="E55">
-        <v>-11.76630439151944</v>
+        <v>-13.14675082259565</v>
       </c>
       <c r="F55">
-        <v>2.751239402419683</v>
+        <v>0.7291225132327955</v>
       </c>
       <c r="G55">
-        <v>-1.630802367677635</v>
+        <v>-2.95456372810169</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.935421865492648</v>
       </c>
       <c r="E56">
-        <v>-11.90246654798207</v>
+        <v>-13.42358096715854</v>
       </c>
       <c r="F56">
-        <v>2.889283128538963</v>
+        <v>1.243974220400752</v>
       </c>
       <c r="G56">
-        <v>-1.87311443787905</v>
+        <v>-3.501578409737625</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.447787671828192</v>
       </c>
       <c r="E57">
-        <v>-10.06929045646303</v>
+        <v>-12.45700988953936</v>
       </c>
       <c r="F57">
-        <v>3.220892142760998</v>
+        <v>1.123406689058347</v>
       </c>
       <c r="G57">
-        <v>-1.887793396800179</v>
+        <v>-3.551541163016307</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.958176842709291</v>
       </c>
       <c r="E58">
-        <v>-9.915213656826049</v>
+        <v>-11.25314224544424</v>
       </c>
       <c r="F58">
-        <v>2.844022397181619</v>
+        <v>0.9535573970392969</v>
       </c>
       <c r="G58">
-        <v>-2.2019376841127</v>
+        <v>-4.171036928689045</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.450990367482477</v>
       </c>
       <c r="E59">
-        <v>-9.460754119312282</v>
+        <v>-10.4562712027885</v>
       </c>
       <c r="F59">
-        <v>3.149229450087363</v>
+        <v>1.075494833998557</v>
       </c>
       <c r="G59">
-        <v>-2.332945902738279</v>
+        <v>-3.824495642729216</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.917364143572126</v>
       </c>
       <c r="E60">
-        <v>-8.315489457350425</v>
+        <v>-10.76200659694235</v>
       </c>
       <c r="F60">
-        <v>2.862540670450852</v>
+        <v>1.010950899414822</v>
       </c>
       <c r="G60">
-        <v>-2.84427621400641</v>
+        <v>-4.01625568254596</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.346222325753546</v>
       </c>
       <c r="E61">
-        <v>-8.681852061518974</v>
+        <v>-10.56804752671982</v>
       </c>
       <c r="F61">
-        <v>2.815967046889609</v>
+        <v>0.5288043031066062</v>
       </c>
       <c r="G61">
-        <v>-3.214282646748593</v>
+        <v>-3.840204181313057</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.726030719972092</v>
       </c>
       <c r="E62">
-        <v>-8.0892967091413</v>
+        <v>-10.88219229710592</v>
       </c>
       <c r="F62">
-        <v>3.005582572439259</v>
+        <v>1.063925862286272</v>
       </c>
       <c r="G62">
-        <v>-2.942397473244869</v>
+        <v>-4.640392833064757</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.05627624877453</v>
       </c>
       <c r="E63">
-        <v>-8.383996212138463</v>
+        <v>-9.8824184480625</v>
       </c>
       <c r="F63">
-        <v>3.113228647217593</v>
+        <v>1.10529226079755</v>
       </c>
       <c r="G63">
-        <v>-3.0874291627748</v>
+        <v>-4.706083988200515</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.33112938733485</v>
       </c>
       <c r="E64">
-        <v>-6.918405412770037</v>
+        <v>-9.176442935688714</v>
       </c>
       <c r="F64">
-        <v>2.674014734571025</v>
+        <v>0.5202792141637956</v>
       </c>
       <c r="G64">
-        <v>-2.918028547530294</v>
+        <v>-4.864526697710034</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.55129902037929</v>
       </c>
       <c r="E65">
-        <v>-6.868198221446995</v>
+        <v>-9.341225047879824</v>
       </c>
       <c r="F65">
-        <v>2.762854301603516</v>
+        <v>0.7954576192068923</v>
       </c>
       <c r="G65">
-        <v>-3.67398831087733</v>
+        <v>-4.76606776282657</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.72054328077314</v>
       </c>
       <c r="E66">
-        <v>-6.542401687439159</v>
+        <v>-8.167421942721628</v>
       </c>
       <c r="F66">
-        <v>2.512570169845212</v>
+        <v>0.5836464552523588</v>
       </c>
       <c r="G66">
-        <v>-3.822525868133349</v>
+        <v>-4.556705552377521</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.84044701500959</v>
       </c>
       <c r="E67">
-        <v>-7.274017419644374</v>
+        <v>-7.919143826777094</v>
       </c>
       <c r="F67">
-        <v>2.522210187752493</v>
+        <v>0.4720624957152839</v>
       </c>
       <c r="G67">
-        <v>-4.313214927964125</v>
+        <v>-5.303187223845623</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.9201647792669</v>
       </c>
       <c r="E68">
-        <v>-5.663470167290419</v>
+        <v>-8.989272048003683</v>
       </c>
       <c r="F68">
-        <v>2.430591216838405</v>
+        <v>0.02108164811700055</v>
       </c>
       <c r="G68">
-        <v>-4.329529296381653</v>
+        <v>-5.165852552694497</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.96331346154964</v>
       </c>
       <c r="E69">
-        <v>-7.136184256272911</v>
+        <v>-9.00004528766793</v>
       </c>
       <c r="F69">
-        <v>2.164877038345975</v>
+        <v>0.1715899316437462</v>
       </c>
       <c r="G69">
-        <v>-4.23392405175304</v>
+        <v>-5.793760414582525</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.97394507441868</v>
       </c>
       <c r="E70">
-        <v>-6.022161536489973</v>
+        <v>-8.369219801451434</v>
       </c>
       <c r="F70">
-        <v>2.050474874132375</v>
+        <v>0.07115209433953412</v>
       </c>
       <c r="G70">
-        <v>-4.582852241046684</v>
+        <v>-5.450665406529076</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.95875421985918</v>
       </c>
       <c r="E71">
-        <v>-5.626155541467216</v>
+        <v>-7.674796426271216</v>
       </c>
       <c r="F71">
-        <v>1.886214480288911</v>
+        <v>0.1835619565115107</v>
       </c>
       <c r="G71">
-        <v>-4.35684129708064</v>
+        <v>-5.356391001207251</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.91463488004379</v>
       </c>
       <c r="E72">
-        <v>-7.022048597383588</v>
+        <v>-8.601109369962211</v>
       </c>
       <c r="F72">
-        <v>1.568626014536261</v>
+        <v>-0.3305113591990071</v>
       </c>
       <c r="G72">
-        <v>-4.424495605721186</v>
+        <v>-5.763647692357313</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.84267325863216</v>
       </c>
       <c r="E73">
-        <v>-6.352042754052728</v>
+        <v>-8.027569079942745</v>
       </c>
       <c r="F73">
-        <v>1.493149758018248</v>
+        <v>0.03379880661797931</v>
       </c>
       <c r="G73">
-        <v>-3.741381086420273</v>
+        <v>-5.077702656620324</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.74012314103337</v>
       </c>
       <c r="E74">
-        <v>-5.616066101378126</v>
+        <v>-8.605207638939152</v>
       </c>
       <c r="F74">
-        <v>1.240189163262851</v>
+        <v>-0.03838413344887754</v>
       </c>
       <c r="G74">
-        <v>-4.102369593113482</v>
+        <v>-4.546141601561706</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.60690721899939</v>
       </c>
       <c r="E75">
-        <v>-5.976052614143874</v>
+        <v>-8.746948875379235</v>
       </c>
       <c r="F75">
-        <v>1.334536859469241</v>
+        <v>-0.2187231015988406</v>
       </c>
       <c r="G75">
-        <v>-3.665546419752188</v>
+        <v>-4.006741174666095</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.44915606364682</v>
       </c>
       <c r="E76">
-        <v>-6.168272750347457</v>
+        <v>-9.642508952084141</v>
       </c>
       <c r="F76">
-        <v>0.9269733095427303</v>
+        <v>-0.6861253958343155</v>
       </c>
       <c r="G76">
-        <v>-3.709361489964442</v>
+        <v>-5.021671673368159</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.26746751772249</v>
       </c>
       <c r="E77">
-        <v>-7.322540018636563</v>
+        <v>-10.66121635095363</v>
       </c>
       <c r="F77">
-        <v>1.057491265151842</v>
+        <v>-0.4587139367597459</v>
       </c>
       <c r="G77">
-        <v>-3.769143321312602</v>
+        <v>-5.190151956952748</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.06806658103638</v>
       </c>
       <c r="E78">
-        <v>-7.723645075391956</v>
+        <v>-10.3524242368446</v>
       </c>
       <c r="F78">
-        <v>1.383098033954361</v>
+        <v>-0.9910172912628871</v>
       </c>
       <c r="G78">
-        <v>-3.796912177296008</v>
+        <v>-4.715840165904747</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.857292104008881</v>
       </c>
       <c r="E79">
-        <v>-7.053095815180176</v>
+        <v>-10.57973551813362</v>
       </c>
       <c r="F79">
-        <v>1.044487455880168</v>
+        <v>-0.7093472756724042</v>
       </c>
       <c r="G79">
-        <v>-3.086187708197573</v>
+        <v>-4.188056443306438</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.63505935800392</v>
       </c>
       <c r="E80">
-        <v>-8.407399365810104</v>
+        <v>-11.60106943192756</v>
       </c>
       <c r="F80">
-        <v>0.7331324566106883</v>
+        <v>-0.7535342544190802</v>
       </c>
       <c r="G80">
-        <v>-3.444401977728873</v>
+        <v>-3.452833937217397</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.40670676448827</v>
       </c>
       <c r="E81">
-        <v>-10.16766249733165</v>
+        <v>-11.81422923194261</v>
       </c>
       <c r="F81">
-        <v>0.9856638670630008</v>
+        <v>-0.9469324615477569</v>
       </c>
       <c r="G81">
-        <v>-2.724308664754301</v>
+        <v>-3.347551967977494</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.170726552978989</v>
       </c>
       <c r="E82">
-        <v>-10.38107136341712</v>
+        <v>-11.93238164727674</v>
       </c>
       <c r="F82">
-        <v>0.4488382403183221</v>
+        <v>-0.951495118290138</v>
       </c>
       <c r="G82">
-        <v>-2.6871577227126</v>
+        <v>-3.937160128521693</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.929569729839779</v>
       </c>
       <c r="E83">
-        <v>-12.21507616567957</v>
+        <v>-14.00300827338798</v>
       </c>
       <c r="F83">
-        <v>0.4654687361363518</v>
+        <v>-0.8550862288348039</v>
       </c>
       <c r="G83">
-        <v>-2.31772401434871</v>
+        <v>-3.409068525188232</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.687622442367116</v>
       </c>
       <c r="E84">
-        <v>-11.97378548512887</v>
+        <v>-13.3037077317015</v>
       </c>
       <c r="F84">
-        <v>0.3537921298032237</v>
+        <v>-1.152835610584743</v>
       </c>
       <c r="G84">
-        <v>-1.063447694248417</v>
+        <v>-3.095407577524444</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.442910626365979</v>
       </c>
       <c r="E85">
-        <v>-12.36073000366228</v>
+        <v>-15.33195236957495</v>
       </c>
       <c r="F85">
-        <v>0.2928075742644392</v>
+        <v>-1.177222306123638</v>
       </c>
       <c r="G85">
-        <v>-1.314201655574974</v>
+        <v>-2.968355460818294</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.199742642233975</v>
       </c>
       <c r="E86">
-        <v>-13.56821589848953</v>
+        <v>-13.84513661253258</v>
       </c>
       <c r="F86">
-        <v>0.3859120613272088</v>
+        <v>-1.449854903907666</v>
       </c>
       <c r="G86">
-        <v>-1.083896934044495</v>
+        <v>-2.038529156294274</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.962694995555813</v>
       </c>
       <c r="E87">
-        <v>-15.2734716562399</v>
+        <v>-18.83914227666546</v>
       </c>
       <c r="F87">
-        <v>-0.2376713510241159</v>
+        <v>-1.318679710343647</v>
       </c>
       <c r="G87">
-        <v>-0.5994912896472568</v>
+        <v>-2.389072891811082</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.733235320718035</v>
       </c>
       <c r="E88">
-        <v>-17.97778123566648</v>
+        <v>-19.73716584323053</v>
       </c>
       <c r="F88">
-        <v>-0.1176565330461991</v>
+        <v>-1.420298992260777</v>
       </c>
       <c r="G88">
-        <v>-1.458001822164297</v>
+        <v>-3.016500724595915</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.517601200366071</v>
       </c>
       <c r="E89">
-        <v>-18.28803604687999</v>
+        <v>-20.64931824869954</v>
       </c>
       <c r="F89">
-        <v>-0.06349379073816998</v>
+        <v>-1.159935364203659</v>
       </c>
       <c r="G89">
-        <v>-0.3495517225233608</v>
+        <v>-3.140798467413391</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.313813507971393</v>
       </c>
       <c r="E90">
-        <v>-18.94106464115609</v>
+        <v>-21.22348799660607</v>
       </c>
       <c r="F90">
-        <v>-0.007096439383455816</v>
+        <v>-1.610956596302786</v>
       </c>
       <c r="G90">
-        <v>-0.557768484215822</v>
+        <v>-1.178326935006667</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.122941966545453</v>
       </c>
       <c r="E91">
-        <v>-21.67835509678053</v>
+        <v>-24.1906075650678</v>
       </c>
       <c r="F91">
-        <v>-0.2782237246948583</v>
+        <v>-1.905514810633115</v>
       </c>
       <c r="G91">
-        <v>-0.1642075199617241</v>
+        <v>-2.202871257954774</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.944764535851546</v>
       </c>
       <c r="E92">
-        <v>-24.31549382125133</v>
+        <v>-26.4050902249807</v>
       </c>
       <c r="F92">
-        <v>-0.7796875739066472</v>
+        <v>-1.933241541947671</v>
       </c>
       <c r="G92">
-        <v>-0.2685459837229341</v>
+        <v>-1.61647101603813</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.772495127101849</v>
       </c>
       <c r="E93">
-        <v>-26.14898237747691</v>
+        <v>-27.56443391263241</v>
       </c>
       <c r="F93">
-        <v>-0.5273976786064393</v>
+        <v>-1.85323271909967</v>
       </c>
       <c r="G93">
-        <v>-0.09720207824687524</v>
+        <v>-1.937564138437581</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.603559095311438</v>
       </c>
       <c r="E94">
-        <v>-27.04770785751317</v>
+        <v>-30.31253383571316</v>
       </c>
       <c r="F94">
-        <v>-1.243906619252089</v>
+        <v>-2.151828591661412</v>
       </c>
       <c r="G94">
-        <v>-0.394551968038674</v>
+        <v>-1.443379142517336</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.43470975593267</v>
       </c>
       <c r="E95">
-        <v>-29.79557682841953</v>
+        <v>-31.68032997464894</v>
       </c>
       <c r="F95">
-        <v>-0.6246981944921657</v>
+        <v>-2.149247942872203</v>
       </c>
       <c r="G95">
-        <v>-0.2606569537028508</v>
+        <v>-1.612759894488607</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.260400312252058</v>
       </c>
       <c r="E96">
-        <v>-32.57701537714475</v>
+        <v>-34.15403154370891</v>
       </c>
       <c r="F96">
-        <v>-0.7456695708430079</v>
+        <v>-1.957802445137264</v>
       </c>
       <c r="G96">
-        <v>-0.5383223397181431</v>
+        <v>-2.807737722889474</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.08233548923176</v>
       </c>
       <c r="E97">
-        <v>-34.671851225301</v>
+        <v>-36.13049081706765</v>
       </c>
       <c r="F97">
-        <v>-1.270314123539084</v>
+        <v>-1.722173136067479</v>
       </c>
       <c r="G97">
-        <v>-0.6151700333212452</v>
+        <v>-3.14620789882456</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.895401989511148</v>
       </c>
       <c r="E98">
-        <v>-37.24563886264149</v>
+        <v>-37.81904329844073</v>
       </c>
       <c r="F98">
-        <v>-0.9829538525944271</v>
+        <v>-1.519915678047834</v>
       </c>
       <c r="G98">
-        <v>-0.5276193459896793</v>
+        <v>-1.848000639418139</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.705793631783002</v>
       </c>
       <c r="E99">
-        <v>-39.33518092468277</v>
+        <v>-41.75884512019499</v>
       </c>
       <c r="F99">
-        <v>-1.125661592634676</v>
+        <v>-2.206437147184638</v>
       </c>
       <c r="G99">
-        <v>-0.9976737754741773</v>
+        <v>-2.635456933025801</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.514329607224028</v>
       </c>
       <c r="E100">
-        <v>-42.31825430707352</v>
+        <v>-43.73955889488393</v>
       </c>
       <c r="F100">
-        <v>-1.137950358685528</v>
+        <v>-2.003432179972905</v>
       </c>
       <c r="G100">
-        <v>-1.037483085583913</v>
+        <v>-2.598620492810331</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.329403021877592</v>
       </c>
       <c r="E101">
-        <v>-45.46780118669724</v>
+        <v>-45.70477170304463</v>
       </c>
       <c r="F101">
-        <v>-1.128102875303326</v>
+        <v>-2.198164659335339</v>
       </c>
       <c r="G101">
-        <v>-1.488564778582848</v>
+        <v>-2.681264951652697</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.142501964207762</v>
       </c>
       <c r="E102">
-        <v>-47.19625858102592</v>
+        <v>-48.49465359155715</v>
       </c>
       <c r="F102">
-        <v>-1.084352999389311</v>
+        <v>-2.468398734510434</v>
       </c>
       <c r="G102">
-        <v>-1.572530145095383</v>
+        <v>-2.73062518564323</v>
       </c>
     </row>
   </sheetData>
